--- a/grafik.xlsx
+++ b/grafik.xlsx
@@ -2,28 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr/>
+  <workbookPr codeName="BuÇalışmaKitabı"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Documents\Mesai Programı APK\web-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A9E101-3E5D-4482-967F-F20DED457EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0039F3-507D-4BA0-A78B-5879D90DE691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grafik" sheetId="1" r:id="rId1"/>
+    <sheet name="grafik (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="grafik (3)" sheetId="3" r:id="rId3"/>
+    <sheet name="grafik (4)" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">grafik!$D$2:$R$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'grafik (2)'!$D$2:$R$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'grafik (3)'!$D$2:$R$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'grafik (4)'!$D$2:$R$26</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="25">
   <si>
     <t>Donem Grafigi (24.03.2026 - 23.04.2026)</t>
   </si>
@@ -293,6 +299,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -344,6 +355,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -395,6 +411,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -446,6 +467,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -497,6 +523,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -548,6 +579,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -602,6 +638,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -656,6 +697,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -710,6 +756,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -764,6 +815,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -818,6 +874,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -872,6 +933,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
@@ -929,6 +995,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
@@ -986,6 +1057,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
@@ -1043,6 +1119,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
@@ -1100,6 +1181,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
@@ -1157,6 +1243,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="17"/>
@@ -1214,6 +1305,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="18"/>
@@ -1268,6 +1364,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="19"/>
@@ -1322,6 +1423,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="20"/>
@@ -1376,6 +1482,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="21"/>
@@ -1430,6 +1541,11 @@
                 <a:bevelT w="63500" h="25400"/>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-FCB5-46AD-ACE3-932597564478}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -1791,12 +1907,5394 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="landscape"/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="tr-TR"/>
+  <c:roundedCorners val="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="tr-TR"/>
+              <a:t>Donem Grafigi (24.03.2026 - 23.04.2026)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="tr-TR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'grafik (2)'!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deger</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent6">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="12"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="13"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="14"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="15"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="16"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="17"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="18"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="19"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="20"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="21"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-BB99-47F5-BDD9-A284AB25CA82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="tr-TR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="1"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'grafik (2)'!$A$3:$A$24</c:f>
+              <c:strCache>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>Mehmet TÜZNER</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Zeki KAĞNICI</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sami KAR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Hüseyin ADIGÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Feyzullah YÜCE</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Mustafa İPEK</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Halil ÇETİNKAYA</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Ahmet Talha ÖLMEZ</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alim ARI</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Ferhat ALTINKAYA</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Ömer Furkan KARAARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Furkan ÇEPEL</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Hasan Hüseyin AYGÜN</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>İsmail ÜNAL</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Muhammed Ali ATAY</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Naci GÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Oğuz SEVİM</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Osman ÇATALTEPE</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Osman ERDURAN</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Osman KOÇLUK</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Abdul Samet ŞABAN</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Yusuf Emre KALELİ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'grafik (2)'!$B$3:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000002C-BB99-47F5-BDD9-A284AB25CA82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+        </c:dLbls>
+        <c:gapWidth val="115"/>
+        <c:overlap val="-20"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="tr-TR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="tr-TR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="tr-TR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup orientation="landscape"/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="tr-TR"/>
+  <c:roundedCorners val="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="tr-TR"/>
+              <a:t>Donem Grafigi (24.03.2026 - 23.04.2026)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="tr-TR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'grafik (3)'!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deger</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent6">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="12"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="13"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="14"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="15"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="16"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="17"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="18"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="19"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="20"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="21"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-6432-48C1-9B58-6270D8D89BF6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="tr-TR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="1"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'grafik (3)'!$A$3:$A$24</c:f>
+              <c:strCache>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>Mehmet TÜZNER</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Zeki KAĞNICI</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sami KAR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Hüseyin ADIGÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Feyzullah YÜCE</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Mustafa İPEK</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Halil ÇETİNKAYA</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Ahmet Talha ÖLMEZ</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alim ARI</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Ferhat ALTINKAYA</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Ömer Furkan KARAARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Furkan ÇEPEL</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Hasan Hüseyin AYGÜN</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>İsmail ÜNAL</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Muhammed Ali ATAY</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Naci GÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Oğuz SEVİM</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Osman ÇATALTEPE</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Osman ERDURAN</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Osman KOÇLUK</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Abdul Samet ŞABAN</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Yusuf Emre KALELİ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'grafik (3)'!$B$3:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000002C-6432-48C1-9B58-6270D8D89BF6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+        </c:dLbls>
+        <c:gapWidth val="115"/>
+        <c:overlap val="-20"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="tr-TR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="tr-TR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="tr-TR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup orientation="landscape"/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="tr-TR"/>
+  <c:roundedCorners val="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="tr-TR"/>
+              <a:t>Donem Grafigi (24.03.2026 - 23.04.2026)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="tr-TR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'grafik (4)'!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deger</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent6">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="12"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="13"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="14"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="15"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="16"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="17"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="18"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="19"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="20"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="21"/>
+            <c:invertIfNegative val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-6EE7-4CBD-B801-78F20F3BE645}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="tr-TR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="1"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'grafik (4)'!$A$3:$A$24</c:f>
+              <c:strCache>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>Mehmet TÜZNER</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Zeki KAĞNICI</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sami KAR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Hüseyin ADIGÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Feyzullah YÜCE</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Mustafa İPEK</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Halil ÇETİNKAYA</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Ahmet Talha ÖLMEZ</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Alim ARI</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Ferhat ALTINKAYA</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Ömer Furkan KARAARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Furkan ÇEPEL</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Hasan Hüseyin AYGÜN</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>İsmail ÜNAL</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Muhammed Ali ATAY</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Naci GÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Oğuz SEVİM</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Osman ÇATALTEPE</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Osman ERDURAN</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Osman KOÇLUK</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Abdul Samet ŞABAN</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Yusuf Emre KALELİ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'grafik (4)'!$B$3:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000002C-6EE7-4CBD-B801-78F20F3BE645}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+        </c:dLbls>
+        <c:gapWidth val="115"/>
+        <c:overlap val="-20"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="tr-TR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="tr-TR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="tr-TR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup orientation="landscape"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2338,16 +7836,1522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="341">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="341">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="341">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="8640000" cy="3780000"/>
+    <xdr:ext cx="9067800" cy="3780000"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -2358,6 +9362,120 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9067800" cy="3780000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEB72F50-49C6-4BCB-A5FC-A1E44736E7DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9067800" cy="3780000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BAC2FF0-8345-45C9-BEF0-22EAC9F667C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9067800" cy="3780000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{908C2525-90FF-40CC-805B-1DAE4A736540}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2659,6 +9777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sayfa1"/>
   <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2854,7 +9973,616 @@
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD930DD8-8393-4442-AF1E-0AB9191F7A4F}">
+  <sheetPr codeName="Sayfa2"/>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29C6BE67-6871-4CBC-B99A-774E17221F8F}">
+  <sheetPr codeName="Sayfa3"/>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EB0B3A5-DCBE-4ADD-B22A-1777D73F7854}">
+  <sheetPr codeName="Sayfa4"/>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/grafik.xlsx
+++ b/grafik.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Documents\Mesai Programı APK\web-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0039F3-507D-4BA0-A78B-5879D90DE691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96AC25D-53A4-41F1-B31F-39CB38908034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grafik" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,17 @@
     <sheet name="grafik (4)" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">grafik!$D$2:$R$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'grafik (2)'!$D$2:$R$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'grafik (3)'!$D$2:$R$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'grafik (4)'!$D$2:$R$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">grafik!$D$2:$Q$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'grafik (2)'!$D$2:$Q$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'grafik (3)'!$D$2:$Q$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'grafik (4)'!$D$2:$Q$26</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="26">
   <si>
     <t>Donem Grafigi (24.03.2026 - 23.04.2026)</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Yusuf Emre KALELİ</t>
+  </si>
+  <si>
+    <t>"</t>
   </si>
 </sst>
 </file>
@@ -10184,7 +10187,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29C6BE67-6871-4CBC-B99A-774E17221F8F}">
   <sheetPr codeName="Sayfa3"/>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -10312,7 +10315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -10320,7 +10323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -10328,15 +10331,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
+      <c r="Y19" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -10344,7 +10350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -10352,7 +10358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -10360,7 +10366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -10368,7 +10374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>

--- a/grafik.xlsx
+++ b/grafik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Documents\Mesai Programı APK\web-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96AC25D-53A4-41F1-B31F-39CB38908034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3C060C-7580-4CFF-BEB9-E5C97C4C204E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1792,7 +1792,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3546,7 +3546,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -5300,7 +5300,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -7054,7 +7054,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>

--- a/grafik.xlsx
+++ b/grafik.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="BuÇalışmaKitabı"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Documents\Mesai Programı APK\web-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7697EEF8-B55A-4513-A064-05ADE058415F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AED8F5-56D1-4BE3-BE23-A2DCAEBFFD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grafik" sheetId="1" r:id="rId1"/>
@@ -1605,7 +1605,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3102,7 +3102,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4599,7 +4599,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -6096,7 +6096,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="700" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>

--- a/grafik.xlsx
+++ b/grafik.xlsx
@@ -1,35 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="BuÇalışmaKitabı"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Documents\Mesai Programı APK\web-portal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehme\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8F70A5-4DC4-426A-9AD8-23BE08C0596A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A3A179-8B54-4972-A63B-944EF2D3D479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="grafik" sheetId="1" r:id="rId1"/>
-    <sheet name="grafik (2)" sheetId="2" r:id="rId2"/>
-    <sheet name="grafik (3)" sheetId="3" r:id="rId3"/>
+    <sheet name="grafik" sheetId="5" r:id="rId1"/>
+    <sheet name="grafik (2) " sheetId="6" r:id="rId2"/>
+    <sheet name="grafik (3)" sheetId="7" r:id="rId3"/>
     <sheet name="grafik (4)" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">grafik!$D$2:$Q$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'grafik (2)'!$D$2:$Q$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'grafik (3)'!$D$2:$Q$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'grafik (4)'!$D$2:$Q$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">grafik!$D$2:$S$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'grafik (2) '!$D$2:$S$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'grafik (3)'!$D$2:$S$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'grafik (4)'!$D$2:$S$39</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="3">
   <si>
     <t>Donem Grafigi (24.03.2026 - 23.04.2026)</t>
   </si>
@@ -38,135 +38,6 @@
   </si>
   <si>
     <t>Deger</t>
-  </si>
-  <si>
-    <t>Hüseyin ADIGÜZEL</t>
-  </si>
-  <si>
-    <t>Zeki KAĞNICI</t>
-  </si>
-  <si>
-    <t>Sami KAR</t>
-  </si>
-  <si>
-    <t>Mehmet TÜZNER</t>
-  </si>
-  <si>
-    <t>Yusuf Emre KALELİ</t>
-  </si>
-  <si>
-    <t>Feyzullah YÜCE</t>
-  </si>
-  <si>
-    <t>Yaşar ÇATAL</t>
-  </si>
-  <si>
-    <t>Mustafa ALTUNOK</t>
-  </si>
-  <si>
-    <t>Ahmet Talha ÖLMEZ</t>
-  </si>
-  <si>
-    <t>Alim ARI</t>
-  </si>
-  <si>
-    <t>Yusuf ÇELİK</t>
-  </si>
-  <si>
-    <t>Emre ADAM</t>
-  </si>
-  <si>
-    <t>Emre KAYAN</t>
-  </si>
-  <si>
-    <t>Ersin DURMAZ</t>
-  </si>
-  <si>
-    <t>Samet KARACA</t>
-  </si>
-  <si>
-    <t>Ferhat ALTINKAYA</t>
-  </si>
-  <si>
-    <t>Ömer Furkan KARAARSLAN</t>
-  </si>
-  <si>
-    <t>Furkan ÇEPEL</t>
-  </si>
-  <si>
-    <t>Gökhan DEMİRCİ</t>
-  </si>
-  <si>
-    <t>Halil ÇETİNKAYA</t>
-  </si>
-  <si>
-    <t>Hasan Hüseyin AYGÜN</t>
-  </si>
-  <si>
-    <t>Hasan İNANIR</t>
-  </si>
-  <si>
-    <t>İsmail ARSLAN</t>
-  </si>
-  <si>
-    <t>İsmail ÜNAL</t>
-  </si>
-  <si>
-    <t>Ömer Kaan AKYAVAŞ</t>
-  </si>
-  <si>
-    <t>Kazım ŞEN</t>
-  </si>
-  <si>
-    <t>Muhammet KAYA</t>
-  </si>
-  <si>
-    <t>Mecit ÜYE</t>
-  </si>
-  <si>
-    <t>Muhammed ŞİMŞEK</t>
-  </si>
-  <si>
-    <t>Muhammed Ali ATAY</t>
-  </si>
-  <si>
-    <t>Mustafa İPEK</t>
-  </si>
-  <si>
-    <t>Naci GÜZEL</t>
-  </si>
-  <si>
-    <t>Oğuz SEVİM</t>
-  </si>
-  <si>
-    <t>Osman ÇELİK</t>
-  </si>
-  <si>
-    <t>Osman ÇATALTEPE</t>
-  </si>
-  <si>
-    <t>Osman ERDURAN</t>
-  </si>
-  <si>
-    <t>Osman KOÇLUK</t>
-  </si>
-  <si>
-    <t>Ramazan POLAT</t>
-  </si>
-  <si>
-    <t>Abdul Samet ŞABAN</t>
-  </si>
-  <si>
-    <t>Şahin SEVİNÇ</t>
-  </si>
-  <si>
-    <t>Sefa ÖLMEZ</t>
-  </si>
-  <si>
-    <t>Muhammed TÜRKARSLAN</t>
-  </si>
-  <si>
-    <t>Kamil YILMAZ</t>
   </si>
 </sst>
 </file>
@@ -226,42 +97,32 @@
   <c:date1904 val="0"/>
   <c:lang val="tr-TR"/>
   <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
               <a:rPr lang="tr-TR"/>
-              <a:t>Donem Grafigi (24.03.2026 - 23.04.2026)</a:t>
+              <a:t>Bayram mesaisi (yıl) - 2026 · 57 kişi</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </c:spPr>
+      <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -326,7 +187,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000001-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -366,7 +227,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000003-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -406,7 +267,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000005-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -446,7 +307,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000007-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -486,7 +347,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000009-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -526,7 +387,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000000B-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -569,7 +430,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000000D-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -612,7 +473,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000000F-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -655,7 +516,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000011-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -698,7 +559,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000013-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -741,7 +602,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000015-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -784,7 +645,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000017-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -830,7 +691,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000019-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000019-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -876,7 +737,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001B-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000001B-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -922,7 +783,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001D-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000001D-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -968,7 +829,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001F-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000001F-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1014,7 +875,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000021-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000021-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1060,7 +921,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000023-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000023-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1103,7 +964,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000025-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000025-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1146,7 +1007,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000027-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000027-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1189,7 +1050,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000029-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000029-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1232,7 +1093,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002B-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000002B-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1275,7 +1136,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002D-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000002D-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1318,7 +1179,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002F-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000002F-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1364,7 +1225,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000031-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000031-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1410,7 +1271,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000033-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000033-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1456,7 +1317,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000035-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000035-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1502,7 +1363,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000037-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000037-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1548,7 +1409,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000039-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000039-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1594,7 +1455,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003B-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000003B-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1637,7 +1498,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003D-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000003D-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1680,7 +1541,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003F-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000003F-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1723,7 +1584,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000041-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000041-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1766,7 +1627,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000043-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000043-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1809,7 +1670,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000045-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000045-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1852,7 +1713,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000047-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000047-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1898,7 +1759,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000049-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000049-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1944,7 +1805,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004B-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000004B-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1990,7 +1851,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004D-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000004D-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2036,7 +1897,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004F-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{0000004F-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2082,7 +1943,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000051-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000051-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2128,7 +1989,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000053-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000053-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2171,7 +2032,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000055-545B-471A-AC4A-59809AA550A6}"/>
+                <c16:uniqueId val="{00000055-F106-4CDB-B3D5-24B6A1B15F0F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2184,23 +2045,11 @@
               </a:ln>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr/>
                 </a:pPr>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -2220,283 +2069,26 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
-              <c:f>grafik!$A$3:$A$45</c:f>
-              <c:strCache>
-                <c:ptCount val="43"/>
-                <c:pt idx="0">
-                  <c:v>Hüseyin ADIGÜZEL</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Zeki KAĞNICI</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Sami KAR</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Mehmet TÜZNER</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Yusuf Emre KALELİ</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Feyzullah YÜCE</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Yaşar ÇATAL</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Mustafa ALTUNOK</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Ahmet Talha ÖLMEZ</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alim ARI</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Yusuf ÇELİK</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Emre ADAM</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Emre KAYAN</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Ersin DURMAZ</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Samet KARACA</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Ferhat ALTINKAYA</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Ömer Furkan KARAARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Furkan ÇEPEL</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Gökhan DEMİRCİ</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Halil ÇETİNKAYA</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Hasan Hüseyin AYGÜN</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Hasan İNANIR</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>İsmail ARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>İsmail ÜNAL</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Ömer Kaan AKYAVAŞ</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>Kazım ŞEN</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>Muhammet KAYA</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>Mecit ÜYE</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>Muhammed ŞİMŞEK</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Muhammed Ali ATAY</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>Mustafa İPEK</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>Naci GÜZEL</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>Oğuz SEVİM</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>Osman ÇELİK</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>Osman ÇATALTEPE</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>Osman ERDURAN</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>Osman KOÇLUK</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>Ramazan POLAT</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>Abdul Samet ŞABAN</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>Şahin SEVİNÇ</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>Sefa ÖLMEZ</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>Muhammed TÜRKARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>Kamil YILMAZ</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:numRef>
+              <c:f>grafik!$A$3:$A$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="57"/>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafik!$B$3:$B$45</c:f>
+              <c:f>grafik!$B$3:$B$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
-                <c:pt idx="0">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0</c:v>
-                </c:pt>
+                <c:ptCount val="57"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000056-545B-471A-AC4A-59809AA550A6}"/>
+              <c16:uniqueId val="{00000056-F106-4CDB-B3D5-24B6A1B15F0F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2539,21 +2131,11 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr sz="600"/>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -2598,21 +2180,11 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -2628,23 +2200,37 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="lt1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="dk1"/>
       </a:solidFill>
       <a:prstDash val="solid"/>
-      <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="tr-TR"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-    <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+    <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -2654,42 +2240,32 @@
   <c:date1904 val="0"/>
   <c:lang val="tr-TR"/>
   <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
               <a:rPr lang="tr-TR"/>
-              <a:t>Donem Grafigi (24.03.2026 - 23.04.2026)</a:t>
+              <a:t>Bayram mesaisi (yıl) - 2026 · 57 kişi</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </c:spPr>
+      <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2703,7 +2279,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'grafik (2)'!$B$2</c:f>
+              <c:f>'grafik (2) '!$B$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2754,7 +2330,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000001-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2794,7 +2370,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000003-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2834,7 +2410,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000005-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2874,7 +2450,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000007-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2914,7 +2490,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000009-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2954,7 +2530,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000000B-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2997,7 +2573,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000000D-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3040,7 +2616,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000000F-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3083,7 +2659,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000011-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3126,7 +2702,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000013-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3169,7 +2745,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000015-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3212,7 +2788,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000017-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3258,7 +2834,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000019-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000019-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3304,7 +2880,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001B-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000001B-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3350,7 +2926,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001D-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000001D-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3396,7 +2972,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001F-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000001F-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3442,7 +3018,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000021-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000021-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3488,7 +3064,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000023-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000023-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3531,7 +3107,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000025-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000025-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3574,7 +3150,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000027-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000027-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3617,7 +3193,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000029-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000029-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3660,7 +3236,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002B-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000002B-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3703,7 +3279,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002D-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000002D-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3746,7 +3322,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002F-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000002F-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3792,7 +3368,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000031-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000031-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3838,7 +3414,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000033-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000033-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3884,7 +3460,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000035-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000035-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3930,7 +3506,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000037-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000037-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3976,7 +3552,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000039-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000039-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4022,7 +3598,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003B-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000003B-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4065,7 +3641,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003D-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000003D-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4108,7 +3684,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003F-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000003F-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4151,7 +3727,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000041-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000041-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4194,7 +3770,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000043-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000043-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4237,7 +3813,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000045-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000045-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4280,7 +3856,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000047-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000047-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4326,7 +3902,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000049-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000049-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4372,7 +3948,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004B-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000004B-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4418,7 +3994,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004D-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000004D-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4464,7 +4040,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004F-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{0000004F-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4510,7 +4086,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000051-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000051-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4556,7 +4132,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000053-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000053-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4599,7 +4175,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000055-F529-4157-83B9-0C9A00267D8D}"/>
+                <c16:uniqueId val="{00000055-F33C-454A-975D-12B0FA669D22}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4612,23 +4188,11 @@
               </a:ln>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr/>
                 </a:pPr>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4648,283 +4212,26 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
-              <c:f>'grafik (2)'!$A$3:$A$45</c:f>
-              <c:strCache>
-                <c:ptCount val="43"/>
-                <c:pt idx="0">
-                  <c:v>Hüseyin ADIGÜZEL</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Zeki KAĞNICI</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Sami KAR</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Mehmet TÜZNER</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Yusuf Emre KALELİ</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Feyzullah YÜCE</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Yaşar ÇATAL</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Mustafa ALTUNOK</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Ahmet Talha ÖLMEZ</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alim ARI</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Yusuf ÇELİK</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Emre ADAM</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Emre KAYAN</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Ersin DURMAZ</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Samet KARACA</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Ferhat ALTINKAYA</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Ömer Furkan KARAARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Furkan ÇEPEL</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Gökhan DEMİRCİ</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Halil ÇETİNKAYA</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Hasan Hüseyin AYGÜN</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Hasan İNANIR</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>İsmail ARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>İsmail ÜNAL</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Ömer Kaan AKYAVAŞ</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>Kazım ŞEN</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>Muhammet KAYA</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>Mecit ÜYE</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>Muhammed ŞİMŞEK</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Muhammed Ali ATAY</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>Mustafa İPEK</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>Naci GÜZEL</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>Oğuz SEVİM</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>Osman ÇELİK</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>Osman ÇATALTEPE</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>Osman ERDURAN</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>Osman KOÇLUK</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>Ramazan POLAT</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>Abdul Samet ŞABAN</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>Şahin SEVİNÇ</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>Sefa ÖLMEZ</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>Muhammed TÜRKARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>Kamil YILMAZ</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:numRef>
+              <c:f>'grafik (2) '!$A$3:$A$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="57"/>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'grafik (2)'!$B$3:$B$45</c:f>
+              <c:f>'grafik (2) '!$B$3:$B$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
-                <c:pt idx="0">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0</c:v>
-                </c:pt>
+                <c:ptCount val="57"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000056-F529-4157-83B9-0C9A00267D8D}"/>
+              <c16:uniqueId val="{00000056-F33C-454A-975D-12B0FA669D22}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4967,21 +4274,11 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr sz="600"/>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5026,21 +4323,11 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5056,23 +4343,37 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="lt1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="dk1"/>
       </a:solidFill>
       <a:prstDash val="solid"/>
-      <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="tr-TR"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-    <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+    <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -5082,42 +4383,32 @@
   <c:date1904 val="0"/>
   <c:lang val="tr-TR"/>
   <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
               <a:rPr lang="tr-TR"/>
-              <a:t>Donem Grafigi (24.03.2026 - 23.04.2026)</a:t>
+              <a:t>Bayram mesaisi (yıl) - 2026 · 57 kişi</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </c:spPr>
+      <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -5182,7 +4473,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000001-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5222,7 +4513,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000003-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5262,7 +4553,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000005-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5302,7 +4593,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000007-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5342,7 +4633,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000009-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5382,7 +4673,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000000B-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5425,7 +4716,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000000D-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5468,7 +4759,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000000F-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5511,7 +4802,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000011-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5554,7 +4845,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000013-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5597,7 +4888,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000015-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5640,7 +4931,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000017-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5686,7 +4977,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000019-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000019-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5732,7 +5023,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001B-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000001B-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5778,7 +5069,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001D-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000001D-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5824,7 +5115,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001F-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000001F-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5870,7 +5161,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000021-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000021-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5916,7 +5207,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000023-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000023-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5959,7 +5250,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000025-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000025-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6002,7 +5293,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000027-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000027-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6045,7 +5336,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000029-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000029-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6088,7 +5379,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002B-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000002B-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6131,7 +5422,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002D-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000002D-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6174,7 +5465,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002F-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000002F-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6220,7 +5511,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000031-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000031-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6266,7 +5557,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000033-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000033-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6312,7 +5603,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000035-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000035-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6358,7 +5649,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000037-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000037-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6404,7 +5695,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000039-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000039-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6450,7 +5741,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003B-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000003B-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6493,7 +5784,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003D-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000003D-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6536,7 +5827,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003F-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000003F-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6579,7 +5870,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000041-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000041-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6622,7 +5913,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000043-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000043-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6665,7 +5956,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000045-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000045-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6708,7 +5999,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000047-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000047-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6754,7 +6045,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000049-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000049-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6800,7 +6091,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004B-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000004B-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6846,7 +6137,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004D-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000004D-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6892,7 +6183,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004F-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{0000004F-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6938,7 +6229,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000051-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000051-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6984,7 +6275,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000053-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000053-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7027,7 +6318,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000055-3486-4A71-9FBE-00E5E7A6293E}"/>
+                <c16:uniqueId val="{00000055-CF78-408B-88E7-FB8E423996E3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7040,23 +6331,11 @@
               </a:ln>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr/>
                 </a:pPr>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -7076,283 +6355,26 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
-              <c:f>'grafik (3)'!$A$3:$A$45</c:f>
-              <c:strCache>
-                <c:ptCount val="43"/>
-                <c:pt idx="0">
-                  <c:v>Hüseyin ADIGÜZEL</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Zeki KAĞNICI</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Sami KAR</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Mehmet TÜZNER</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Yusuf Emre KALELİ</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Feyzullah YÜCE</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Yaşar ÇATAL</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Mustafa ALTUNOK</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Ahmet Talha ÖLMEZ</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alim ARI</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Yusuf ÇELİK</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Emre ADAM</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Emre KAYAN</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Ersin DURMAZ</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Samet KARACA</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Ferhat ALTINKAYA</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Ömer Furkan KARAARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Furkan ÇEPEL</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Gökhan DEMİRCİ</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Halil ÇETİNKAYA</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Hasan Hüseyin AYGÜN</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Hasan İNANIR</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>İsmail ARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>İsmail ÜNAL</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Ömer Kaan AKYAVAŞ</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>Kazım ŞEN</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>Muhammet KAYA</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>Mecit ÜYE</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>Muhammed ŞİMŞEK</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Muhammed Ali ATAY</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>Mustafa İPEK</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>Naci GÜZEL</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>Oğuz SEVİM</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>Osman ÇELİK</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>Osman ÇATALTEPE</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>Osman ERDURAN</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>Osman KOÇLUK</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>Ramazan POLAT</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>Abdul Samet ŞABAN</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>Şahin SEVİNÇ</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>Sefa ÖLMEZ</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>Muhammed TÜRKARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>Kamil YILMAZ</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:numRef>
+              <c:f>'grafik (3)'!$A$3:$A$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="57"/>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'grafik (3)'!$B$3:$B$45</c:f>
+              <c:f>'grafik (3)'!$B$3:$B$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
-                <c:pt idx="0">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0</c:v>
-                </c:pt>
+                <c:ptCount val="57"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000056-3486-4A71-9FBE-00E5E7A6293E}"/>
+              <c16:uniqueId val="{00000056-CF78-408B-88E7-FB8E423996E3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7395,21 +6417,11 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr sz="600"/>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -7454,21 +6466,11 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -7484,23 +6486,37 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="lt1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="dk1"/>
       </a:solidFill>
       <a:prstDash val="solid"/>
-      <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="tr-TR"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-    <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+    <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -7515,37 +6531,20 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
               <a:rPr lang="tr-TR"/>
-              <a:t>Donem Grafigi (24.03.2026 - 23.04.2026)</a:t>
+              <a:t>Bayram mesaisi (yıl) - 2026 · 57 kişi</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </c:spPr>
+      <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -7610,7 +6609,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000001-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7650,7 +6649,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000003-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7690,7 +6689,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000005-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7730,7 +6729,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000007-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7770,7 +6769,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000009-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7810,7 +6809,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000000B-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7853,7 +6852,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000000D-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7896,7 +6895,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000000F-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7939,7 +6938,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000011-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7982,7 +6981,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000013-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8025,7 +7024,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000015-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8068,7 +7067,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000017-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8114,7 +7113,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000019-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000019-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8160,7 +7159,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001B-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000001B-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8206,7 +7205,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001D-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000001D-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8252,7 +7251,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001F-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000001F-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8298,7 +7297,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000021-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000021-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8344,7 +7343,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000023-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000023-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8387,7 +7386,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000025-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000025-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8430,7 +7429,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000027-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000027-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8473,7 +7472,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000029-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000029-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8516,7 +7515,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002B-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000002B-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8559,7 +7558,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002D-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000002D-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8602,7 +7601,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002F-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000002F-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8648,7 +7647,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000031-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000031-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8694,7 +7693,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000033-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000033-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8740,7 +7739,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000035-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000035-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8786,7 +7785,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000037-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000037-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8832,7 +7831,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000039-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000039-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8878,7 +7877,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003B-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000003B-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8921,7 +7920,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003D-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000003D-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8964,7 +7963,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003F-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000003F-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9007,7 +8006,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000041-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000041-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9050,7 +8049,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000043-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000043-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9093,7 +8092,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000045-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000045-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9136,7 +8135,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000047-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000047-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9182,7 +8181,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000049-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000049-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9228,7 +8227,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004B-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000004B-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9274,7 +8273,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004D-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000004D-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9320,7 +8319,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004F-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{0000004F-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9366,7 +8365,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000051-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000051-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9412,7 +8411,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000053-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000053-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9455,7 +8454,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000055-02B0-4882-948E-8B76DDC97A3E}"/>
+                <c16:uniqueId val="{00000055-AEB9-4C41-A713-6D81DCD77F0A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -9468,23 +8467,11 @@
               </a:ln>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
+                  <a:defRPr/>
                 </a:pPr>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -9504,283 +8491,26 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
-              <c:f>'grafik (4)'!$A$3:$A$45</c:f>
-              <c:strCache>
-                <c:ptCount val="43"/>
-                <c:pt idx="0">
-                  <c:v>Hüseyin ADIGÜZEL</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Zeki KAĞNICI</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Sami KAR</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Mehmet TÜZNER</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Yusuf Emre KALELİ</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Feyzullah YÜCE</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Yaşar ÇATAL</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Mustafa ALTUNOK</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Ahmet Talha ÖLMEZ</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alim ARI</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Yusuf ÇELİK</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Emre ADAM</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Emre KAYAN</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Ersin DURMAZ</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Samet KARACA</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Ferhat ALTINKAYA</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Ömer Furkan KARAARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Furkan ÇEPEL</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Gökhan DEMİRCİ</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Halil ÇETİNKAYA</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Hasan Hüseyin AYGÜN</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Hasan İNANIR</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>İsmail ARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>İsmail ÜNAL</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Ömer Kaan AKYAVAŞ</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>Kazım ŞEN</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>Muhammet KAYA</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>Mecit ÜYE</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>Muhammed ŞİMŞEK</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Muhammed Ali ATAY</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>Mustafa İPEK</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>Naci GÜZEL</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>Oğuz SEVİM</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>Osman ÇELİK</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>Osman ÇATALTEPE</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>Osman ERDURAN</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>Osman KOÇLUK</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>Ramazan POLAT</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>Abdul Samet ŞABAN</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>Şahin SEVİNÇ</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>Sefa ÖLMEZ</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>Muhammed TÜRKARSLAN</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>Kamil YILMAZ</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:numRef>
+              <c:f>'grafik (4)'!$A$3:$A$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="57"/>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'grafik (4)'!$B$3:$B$45</c:f>
+              <c:f>'grafik (4)'!$B$3:$B$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
-                <c:pt idx="0">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0</c:v>
-                </c:pt>
+                <c:ptCount val="57"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000056-02B0-4882-948E-8B76DDC97A3E}"/>
+              <c16:uniqueId val="{00000056-AEB9-4C41-A713-6D81DCD77F0A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9823,21 +8553,11 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr sz="600"/>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -9882,21 +8602,11 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -9912,23 +8622,37 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="lt1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="dk1"/>
       </a:solidFill>
       <a:prstDash val="solid"/>
-      <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="tr-TR"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-    <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+    <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -9938,21 +8662,23 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:rowOff>17530</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9067800" cy="6115051"/>
+    <xdr:ext cx="10071100" cy="7135381"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C263F29C-1504-46B7-9DCD-50846636B76B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -9974,21 +8700,23 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:rowOff>17530</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9067800" cy="6115051"/>
+    <xdr:ext cx="10071100" cy="7135381"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EF02066-C6BD-4C4B-99E0-FE5BDCE82C6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -10010,21 +8738,23 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:rowOff>17530</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9067800" cy="6115051"/>
+    <xdr:ext cx="10071100" cy="7135381"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DE16833-E5FC-4DEC-93A2-F543330AFAF6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -10046,11 +8776,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:rowOff>17530</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9067800" cy="6115051"/>
+    <xdr:ext cx="10071100" cy="7135381"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -10361,17 +9091,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sayfa1"/>
-  <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3067CFC-EA40-4B5B-B74F-10E93F9F15C7}">
+  <dimension ref="A1:B39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="6.08984375" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" customWidth="1"/>
+    <col min="19" max="19" width="13.1796875" customWidth="1"/>
+    <col min="20" max="20" width="6.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10379,369 +9115,33 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="39" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4113DB6B-769F-4E94-9ABD-4BA337E64728}">
+  <dimension ref="A1:B39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="6.08984375" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" customWidth="1"/>
+    <col min="19" max="19" width="13.1796875" customWidth="1"/>
+    <col min="20" max="20" width="6.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10749,369 +9149,33 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="39" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{870247E1-7303-4C19-A08B-D6FB23BBF452}">
+  <dimension ref="A1:B39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="6.08984375" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" customWidth="1"/>
+    <col min="19" max="19" width="13.1796875" customWidth="1"/>
+    <col min="20" max="20" width="6.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11119,369 +9183,33 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="39" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="6.08984375" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" customWidth="1"/>
+    <col min="19" max="19" width="13.1796875" customWidth="1"/>
+    <col min="20" max="20" width="6.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11489,354 +9217,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="39" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/grafik.xlsx
+++ b/grafik.xlsx
@@ -5,31 +5,31 @@
   <workbookPr codeName="BuÇalışmaKitabı"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehme\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehme\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A3A179-8B54-4972-A63B-944EF2D3D479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98E7950-E689-4535-BC90-FC4EEA4F47F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="grafik" sheetId="5" r:id="rId1"/>
-    <sheet name="grafik (2) " sheetId="6" r:id="rId2"/>
-    <sheet name="grafik (3)" sheetId="7" r:id="rId3"/>
-    <sheet name="grafik (4)" sheetId="4" r:id="rId4"/>
+    <sheet name="grafik" sheetId="1" r:id="rId1"/>
+    <sheet name="grafik (2)" sheetId="5" r:id="rId2"/>
+    <sheet name="grafik (3)" sheetId="6" r:id="rId3"/>
+    <sheet name="grafik (4)" sheetId="7" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">grafik!$D$2:$S$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'grafik (2) '!$D$2:$S$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'grafik (3)'!$D$2:$S$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'grafik (4)'!$D$2:$S$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">grafik!$D$2:$R$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'grafik (2)'!$D$2:$R$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'grafik (3)'!$D$2:$R$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'grafik (4)'!$D$2:$R$41</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="46">
   <si>
     <t>Donem Grafigi (24.03.2026 - 23.04.2026)</t>
   </si>
@@ -38,6 +38,135 @@
   </si>
   <si>
     <t>Deger</t>
+  </si>
+  <si>
+    <t>Hüseyin ADIGÜZEL</t>
+  </si>
+  <si>
+    <t>Zeki KAĞNICI</t>
+  </si>
+  <si>
+    <t>Sami KAR</t>
+  </si>
+  <si>
+    <t>Mehmet TÜZNER</t>
+  </si>
+  <si>
+    <t>Yusuf Emre KALELİ</t>
+  </si>
+  <si>
+    <t>Feyzullah YÜCE</t>
+  </si>
+  <si>
+    <t>Yaşar ÇATAL</t>
+  </si>
+  <si>
+    <t>Mustafa ALTUNOK</t>
+  </si>
+  <si>
+    <t>Ahmet Talha ÖLMEZ</t>
+  </si>
+  <si>
+    <t>Alim ARI</t>
+  </si>
+  <si>
+    <t>Yusuf ÇELİK</t>
+  </si>
+  <si>
+    <t>Emre ADAM</t>
+  </si>
+  <si>
+    <t>Emre KAYAN</t>
+  </si>
+  <si>
+    <t>Ersin DURMAZ</t>
+  </si>
+  <si>
+    <t>Samet KARACA</t>
+  </si>
+  <si>
+    <t>Ferhat ALTINKAYA</t>
+  </si>
+  <si>
+    <t>Ömer Furkan KARAARSLAN</t>
+  </si>
+  <si>
+    <t>Furkan ÇEPEL</t>
+  </si>
+  <si>
+    <t>Gökhan DEMİRCİ</t>
+  </si>
+  <si>
+    <t>Halil ÇETİNKAYA</t>
+  </si>
+  <si>
+    <t>Hasan Hüseyin AYGÜN</t>
+  </si>
+  <si>
+    <t>Hasan İNANIR</t>
+  </si>
+  <si>
+    <t>İsmail ARSLAN</t>
+  </si>
+  <si>
+    <t>İsmail ÜNAL</t>
+  </si>
+  <si>
+    <t>Ömer Kaan AKYAVAŞ</t>
+  </si>
+  <si>
+    <t>Kazım ŞEN</t>
+  </si>
+  <si>
+    <t>Muhammet KAYA</t>
+  </si>
+  <si>
+    <t>Mecit ÜYE</t>
+  </si>
+  <si>
+    <t>Muhammed ŞİMŞEK</t>
+  </si>
+  <si>
+    <t>Muhammed Ali ATAY</t>
+  </si>
+  <si>
+    <t>Mustafa İPEK</t>
+  </si>
+  <si>
+    <t>Naci GÜZEL</t>
+  </si>
+  <si>
+    <t>Oğuz SEVİM</t>
+  </si>
+  <si>
+    <t>Osman ÇELİK</t>
+  </si>
+  <si>
+    <t>Osman ÇATALTEPE</t>
+  </si>
+  <si>
+    <t>Osman ERDURAN</t>
+  </si>
+  <si>
+    <t>Osman KOÇLUK</t>
+  </si>
+  <si>
+    <t>Ramazan POLAT</t>
+  </si>
+  <si>
+    <t>Abdul Samet ŞABAN</t>
+  </si>
+  <si>
+    <t>Şahin SEVİNÇ</t>
+  </si>
+  <si>
+    <t>Sefa ÖLMEZ</t>
+  </si>
+  <si>
+    <t>Muhammed TÜRKARSLAN</t>
+  </si>
+  <si>
+    <t>Kamil YILMAZ</t>
   </si>
 </sst>
 </file>
@@ -97,32 +226,42 @@
   <c:date1904 val="0"/>
   <c:lang val="tr-TR"/>
   <c:roundedCorners val="1"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr lang="tr-TR"/>
-              <a:t>Bayram mesaisi (yıl) - 2026 · 57 kişi</a:t>
+              <a:t>Donem Grafigi (24.03.2026 - 23.04.2026)</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -187,7 +326,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000001-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -227,7 +366,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000003-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -267,7 +406,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000005-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -307,7 +446,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000007-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -347,7 +486,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000009-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -387,7 +526,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000000B-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -430,7 +569,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000000D-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -473,7 +612,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000000F-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -516,7 +655,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000011-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -559,7 +698,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000013-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -602,7 +741,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000015-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -645,7 +784,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000017-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -691,7 +830,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000019-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000019-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -737,7 +876,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001B-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000001B-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -783,7 +922,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001D-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000001D-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -829,7 +968,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001F-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000001F-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -875,7 +1014,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000021-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000021-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -921,7 +1060,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000023-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000023-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -964,7 +1103,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000025-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000025-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1007,7 +1146,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000027-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000027-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1050,7 +1189,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000029-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000029-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1093,7 +1232,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002B-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000002B-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1136,7 +1275,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002D-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000002D-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1179,7 +1318,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002F-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000002F-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1225,7 +1364,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000031-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000031-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1271,7 +1410,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000033-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000033-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1317,7 +1456,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000035-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000035-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1363,7 +1502,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000037-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000037-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1409,7 +1548,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000039-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000039-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1455,7 +1594,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003B-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000003B-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1498,7 +1637,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003D-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000003D-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1541,7 +1680,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003F-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000003F-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1584,7 +1723,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000041-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000041-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1627,7 +1766,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000043-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000043-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1670,7 +1809,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000045-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000045-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1713,7 +1852,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000047-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000047-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1759,7 +1898,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000049-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000049-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1805,7 +1944,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004B-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000004B-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1851,7 +1990,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004D-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000004D-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1897,7 +2036,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004F-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{0000004F-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1943,7 +2082,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000051-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000051-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1989,7 +2128,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000053-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000053-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2032,7 +2171,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000055-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+                <c16:uniqueId val="{00000055-545B-471A-AC4A-59809AA550A6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2045,11 +2184,23 @@
               </a:ln>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" vert="horz"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -2069,26 +2220,283 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:numRef>
-              <c:f>grafik!$A$3:$A$59</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
-              </c:numCache>
-            </c:numRef>
+            <c:strRef>
+              <c:f>grafik!$A$3:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="43"/>
+                <c:pt idx="0">
+                  <c:v>Hüseyin ADIGÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Zeki KAĞNICI</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sami KAR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Mehmet TÜZNER</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Yusuf Emre KALELİ</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Feyzullah YÜCE</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Yaşar ÇATAL</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mustafa ALTUNOK</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Ahmet Talha ÖLMEZ</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alim ARI</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Yusuf ÇELİK</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Emre ADAM</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Emre KAYAN</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ersin DURMAZ</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Samet KARACA</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Ferhat ALTINKAYA</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Ömer Furkan KARAARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Furkan ÇEPEL</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Gökhan DEMİRCİ</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Halil ÇETİNKAYA</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Hasan Hüseyin AYGÜN</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Hasan İNANIR</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>İsmail ARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>İsmail ÜNAL</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Ömer Kaan AKYAVAŞ</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Kazım ŞEN</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Muhammet KAYA</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Mecit ÜYE</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Muhammed ŞİMŞEK</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Muhammed Ali ATAY</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Mustafa İPEK</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Naci GÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Oğuz SEVİM</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Osman ÇELİK</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Osman ÇATALTEPE</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Osman ERDURAN</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Osman KOÇLUK</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Ramazan POLAT</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Abdul Samet ŞABAN</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Şahin SEVİNÇ</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Sefa ÖLMEZ</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Muhammed TÜRKARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Kamil YILMAZ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>grafik!$B$3:$B$59</c:f>
+              <c:f>grafik!$B$3:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="43"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000056-F106-4CDB-B3D5-24B6A1B15F0F}"/>
+              <c16:uniqueId val="{00000056-545B-471A-AC4A-59809AA550A6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2131,11 +2539,21 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="600"/>
+              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -2180,11 +2598,21 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -2200,36 +2628,22 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr>
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-          <a:latin typeface="+mn-lt"/>
-          <a:ea typeface="+mn-ea"/>
-          <a:cs typeface="+mn-cs"/>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="tr-TR"/>
-    </a:p>
-  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
     <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
   </c:printSettings>
 </c:chartSpace>
@@ -2252,20 +2666,37 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr lang="tr-TR"/>
-              <a:t>Bayram mesaisi (yıl) - 2026 · 57 kişi</a:t>
+              <a:t>Donem Grafigi (24.03.2026 - 23.04.2026)</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2279,7 +2710,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'grafik (2) '!$B$2</c:f>
+              <c:f>'grafik (2)'!$B$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2330,7 +2761,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000001-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2370,7 +2801,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000003-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2410,7 +2841,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000005-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2450,7 +2881,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000007-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2490,7 +2921,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000009-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2530,7 +2961,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000000B-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2573,7 +3004,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000000D-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2616,7 +3047,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000000F-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2659,7 +3090,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000011-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2702,7 +3133,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000013-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2745,7 +3176,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000015-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2788,7 +3219,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000017-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2834,7 +3265,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000019-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000019-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2880,7 +3311,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001B-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000001B-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2926,7 +3357,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001D-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000001D-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2972,7 +3403,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001F-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000001F-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3018,7 +3449,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000021-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000021-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3064,7 +3495,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000023-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000023-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3107,7 +3538,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000025-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000025-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3150,7 +3581,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000027-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000027-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3193,7 +3624,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000029-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000029-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3236,7 +3667,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002B-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000002B-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3279,7 +3710,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002D-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000002D-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3322,7 +3753,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002F-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000002F-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3368,7 +3799,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000031-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000031-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3414,7 +3845,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000033-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000033-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3460,7 +3891,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000035-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000035-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3506,7 +3937,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000037-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000037-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3552,7 +3983,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000039-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000039-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3598,7 +4029,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003B-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000003B-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3641,7 +4072,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003D-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000003D-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3684,7 +4115,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003F-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000003F-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3727,7 +4158,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000041-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000041-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3770,7 +4201,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000043-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000043-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3813,7 +4244,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000045-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000045-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3856,7 +4287,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000047-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000047-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3902,7 +4333,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000049-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000049-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3948,7 +4379,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004B-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000004B-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3994,7 +4425,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004D-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000004D-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4040,7 +4471,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004F-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{0000004F-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4086,7 +4517,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000051-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000051-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4132,7 +4563,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000053-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000053-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4175,7 +4606,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000055-F33C-454A-975D-12B0FA669D22}"/>
+                <c16:uniqueId val="{00000055-3BFA-4389-AD64-B4E0E343E60A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4188,11 +4619,23 @@
               </a:ln>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" vert="horz"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4212,26 +4655,283 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:numRef>
-              <c:f>'grafik (2) '!$A$3:$A$59</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
-              </c:numCache>
-            </c:numRef>
+            <c:strRef>
+              <c:f>'grafik (2)'!$A$3:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="43"/>
+                <c:pt idx="0">
+                  <c:v>Hüseyin ADIGÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Zeki KAĞNICI</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sami KAR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Mehmet TÜZNER</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Yusuf Emre KALELİ</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Feyzullah YÜCE</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Yaşar ÇATAL</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mustafa ALTUNOK</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Ahmet Talha ÖLMEZ</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alim ARI</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Yusuf ÇELİK</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Emre ADAM</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Emre KAYAN</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ersin DURMAZ</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Samet KARACA</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Ferhat ALTINKAYA</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Ömer Furkan KARAARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Furkan ÇEPEL</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Gökhan DEMİRCİ</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Halil ÇETİNKAYA</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Hasan Hüseyin AYGÜN</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Hasan İNANIR</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>İsmail ARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>İsmail ÜNAL</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Ömer Kaan AKYAVAŞ</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Kazım ŞEN</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Muhammet KAYA</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Mecit ÜYE</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Muhammed ŞİMŞEK</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Muhammed Ali ATAY</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Mustafa İPEK</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Naci GÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Oğuz SEVİM</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Osman ÇELİK</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Osman ÇATALTEPE</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Osman ERDURAN</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Osman KOÇLUK</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Ramazan POLAT</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Abdul Samet ŞABAN</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Şahin SEVİNÇ</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Sefa ÖLMEZ</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Muhammed TÜRKARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Kamil YILMAZ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'grafik (2) '!$B$3:$B$59</c:f>
+              <c:f>'grafik (2)'!$B$3:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="43"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000056-F33C-454A-975D-12B0FA669D22}"/>
+              <c16:uniqueId val="{00000056-3BFA-4389-AD64-B4E0E343E60A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4274,11 +4974,21 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="600"/>
+              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -4323,11 +5033,21 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -4343,36 +5063,22 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr>
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-          <a:latin typeface="+mn-lt"/>
-          <a:ea typeface="+mn-ea"/>
-          <a:cs typeface="+mn-cs"/>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="tr-TR"/>
-    </a:p>
-  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
     <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
   </c:printSettings>
 </c:chartSpace>
@@ -4395,20 +5101,37 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr lang="tr-TR"/>
-              <a:t>Bayram mesaisi (yıl) - 2026 · 57 kişi</a:t>
+              <a:t>Donem Grafigi (24.03.2026 - 23.04.2026)</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -4473,7 +5196,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000001-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4513,7 +5236,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000003-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4553,7 +5276,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000005-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4593,7 +5316,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000007-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4633,7 +5356,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000009-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4673,7 +5396,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000000B-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4716,7 +5439,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000000D-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4759,7 +5482,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000000F-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4802,7 +5525,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000011-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4845,7 +5568,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000013-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4888,7 +5611,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000015-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4931,7 +5654,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000017-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4977,7 +5700,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000019-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000019-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5023,7 +5746,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001B-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000001B-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5069,7 +5792,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001D-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000001D-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5115,7 +5838,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001F-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000001F-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5161,7 +5884,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000021-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000021-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5207,7 +5930,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000023-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000023-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5250,7 +5973,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000025-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000025-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5293,7 +6016,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000027-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000027-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5336,7 +6059,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000029-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000029-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5379,7 +6102,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002B-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000002B-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5422,7 +6145,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002D-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000002D-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5465,7 +6188,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002F-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000002F-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5511,7 +6234,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000031-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000031-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5557,7 +6280,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000033-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000033-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5603,7 +6326,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000035-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000035-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5649,7 +6372,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000037-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000037-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5695,7 +6418,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000039-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000039-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5741,7 +6464,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003B-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000003B-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5784,7 +6507,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003D-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000003D-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5827,7 +6550,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003F-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000003F-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5870,7 +6593,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000041-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000041-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5913,7 +6636,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000043-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000043-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5956,7 +6679,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000045-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000045-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5999,7 +6722,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000047-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000047-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6045,7 +6768,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000049-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000049-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6091,7 +6814,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004B-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000004B-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6137,7 +6860,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004D-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000004D-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6183,7 +6906,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004F-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{0000004F-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6229,7 +6952,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000051-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000051-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6275,7 +6998,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000053-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000053-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6318,7 +7041,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000055-CF78-408B-88E7-FB8E423996E3}"/>
+                <c16:uniqueId val="{00000055-96A8-49E6-9346-2619578235F0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6331,11 +7054,23 @@
               </a:ln>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" vert="horz"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -6355,26 +7090,283 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:numRef>
-              <c:f>'grafik (3)'!$A$3:$A$59</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
-              </c:numCache>
-            </c:numRef>
+            <c:strRef>
+              <c:f>'grafik (3)'!$A$3:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="43"/>
+                <c:pt idx="0">
+                  <c:v>Hüseyin ADIGÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Zeki KAĞNICI</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sami KAR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Mehmet TÜZNER</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Yusuf Emre KALELİ</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Feyzullah YÜCE</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Yaşar ÇATAL</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mustafa ALTUNOK</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Ahmet Talha ÖLMEZ</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alim ARI</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Yusuf ÇELİK</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Emre ADAM</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Emre KAYAN</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ersin DURMAZ</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Samet KARACA</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Ferhat ALTINKAYA</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Ömer Furkan KARAARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Furkan ÇEPEL</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Gökhan DEMİRCİ</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Halil ÇETİNKAYA</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Hasan Hüseyin AYGÜN</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Hasan İNANIR</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>İsmail ARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>İsmail ÜNAL</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Ömer Kaan AKYAVAŞ</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Kazım ŞEN</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Muhammet KAYA</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Mecit ÜYE</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Muhammed ŞİMŞEK</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Muhammed Ali ATAY</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Mustafa İPEK</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Naci GÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Oğuz SEVİM</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Osman ÇELİK</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Osman ÇATALTEPE</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Osman ERDURAN</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Osman KOÇLUK</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Ramazan POLAT</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Abdul Samet ŞABAN</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Şahin SEVİNÇ</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Sefa ÖLMEZ</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Muhammed TÜRKARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Kamil YILMAZ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'grafik (3)'!$B$3:$B$59</c:f>
+              <c:f>'grafik (3)'!$B$3:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="43"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000056-CF78-408B-88E7-FB8E423996E3}"/>
+              <c16:uniqueId val="{00000056-96A8-49E6-9346-2619578235F0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6417,11 +7409,21 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="600"/>
+              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -6466,11 +7468,21 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -6486,36 +7498,22 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr>
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-          <a:latin typeface="+mn-lt"/>
-          <a:ea typeface="+mn-ea"/>
-          <a:cs typeface="+mn-cs"/>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="tr-TR"/>
-    </a:p>
-  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
     <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
   </c:printSettings>
 </c:chartSpace>
@@ -6526,25 +7524,49 @@
   <c:date1904 val="0"/>
   <c:lang val="tr-TR"/>
   <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr lang="tr-TR"/>
-              <a:t>Bayram mesaisi (yıl) - 2026 · 57 kişi</a:t>
+              <a:t>Donem Grafigi (24.03.2026 - 23.04.2026)</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -6609,7 +7631,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000001-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6649,7 +7671,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000003-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6689,7 +7711,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000005-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6729,7 +7751,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000007-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6769,7 +7791,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000009-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6809,7 +7831,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000000B-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6852,7 +7874,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000000D-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6895,7 +7917,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000000F-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6938,7 +7960,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000011-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -6981,7 +8003,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000013-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7024,7 +8046,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000015-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7067,7 +8089,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000017-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7113,7 +8135,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000019-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000019-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7159,7 +8181,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001B-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000001B-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7205,7 +8227,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001D-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000001D-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7251,7 +8273,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001F-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000001F-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7297,7 +8319,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000021-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000021-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7343,7 +8365,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000023-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000023-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7386,7 +8408,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000025-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000025-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7429,7 +8451,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000027-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000027-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7472,7 +8494,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000029-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000029-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7515,7 +8537,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002B-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000002B-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7558,7 +8580,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002D-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000002D-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7601,7 +8623,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000002F-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000002F-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7647,7 +8669,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000031-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000031-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7693,7 +8715,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000033-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000033-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7739,7 +8761,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000035-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000035-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7785,7 +8807,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000037-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000037-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7831,7 +8853,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000039-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000039-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7877,7 +8899,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003B-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000003B-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7920,7 +8942,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003D-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000003D-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7963,7 +8985,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003F-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000003F-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8006,7 +9028,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000041-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000041-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8049,7 +9071,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000043-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000043-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8092,7 +9114,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000045-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000045-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8135,7 +9157,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000047-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000047-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8181,7 +9203,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000049-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000049-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8227,7 +9249,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004B-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000004B-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8273,7 +9295,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004D-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000004D-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8319,7 +9341,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004F-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{0000004F-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8365,7 +9387,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000051-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000051-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8411,7 +9433,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000053-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000053-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8454,7 +9476,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000055-AEB9-4C41-A713-6D81DCD77F0A}"/>
+                <c16:uniqueId val="{00000055-175C-458C-8EBD-C95006580191}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -8467,11 +9489,23 @@
               </a:ln>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" vert="horz"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -8491,26 +9525,283 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:numRef>
-              <c:f>'grafik (4)'!$A$3:$A$59</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
-              </c:numCache>
-            </c:numRef>
+            <c:strRef>
+              <c:f>'grafik (4)'!$A$3:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="43"/>
+                <c:pt idx="0">
+                  <c:v>Hüseyin ADIGÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Zeki KAĞNICI</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sami KAR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Mehmet TÜZNER</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Yusuf Emre KALELİ</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Feyzullah YÜCE</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Yaşar ÇATAL</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mustafa ALTUNOK</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Ahmet Talha ÖLMEZ</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Alim ARI</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Yusuf ÇELİK</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Emre ADAM</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Emre KAYAN</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ersin DURMAZ</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Samet KARACA</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Ferhat ALTINKAYA</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Ömer Furkan KARAARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Furkan ÇEPEL</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Gökhan DEMİRCİ</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Halil ÇETİNKAYA</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Hasan Hüseyin AYGÜN</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Hasan İNANIR</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>İsmail ARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>İsmail ÜNAL</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Ömer Kaan AKYAVAŞ</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Kazım ŞEN</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Muhammet KAYA</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Mecit ÜYE</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Muhammed ŞİMŞEK</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Muhammed Ali ATAY</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Mustafa İPEK</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Naci GÜZEL</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Oğuz SEVİM</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Osman ÇELİK</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Osman ÇATALTEPE</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Osman ERDURAN</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Osman KOÇLUK</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Ramazan POLAT</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Abdul Samet ŞABAN</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>Şahin SEVİNÇ</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>Sefa ÖLMEZ</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>Muhammed TÜRKARSLAN</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>Kamil YILMAZ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'grafik (4)'!$B$3:$B$59</c:f>
+              <c:f>'grafik (4)'!$B$3:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="43"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000056-AEB9-4C41-A713-6D81DCD77F0A}"/>
+              <c16:uniqueId val="{00000056-175C-458C-8EBD-C95006580191}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8553,11 +9844,21 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="600"/>
+              <a:defRPr sz="600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -8602,11 +9903,21 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -8622,36 +9933,22 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr>
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-          <a:latin typeface="+mn-lt"/>
-          <a:ea typeface="+mn-ea"/>
-          <a:cs typeface="+mn-cs"/>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="tr-TR"/>
-    </a:p>
-  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+    <c:pageMargins b="0.19685039370078741" l="0.19685039370078741" r="0.19685039370078741" t="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
     <c:pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
   </c:printSettings>
 </c:chartSpace>
@@ -8662,23 +9959,21 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
+      <xdr:colOff>12375</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>17530</xdr:rowOff>
+      <xdr:rowOff>6574</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="10071100" cy="7135381"/>
+    <xdr:ext cx="9635245" cy="7350667"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C263F29C-1504-46B7-9DCD-50846636B76B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -8700,17 +9995,17 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
+      <xdr:colOff>12375</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>17530</xdr:rowOff>
+      <xdr:rowOff>6574</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="10071100" cy="7135381"/>
+    <xdr:ext cx="9635245" cy="7350667"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EF02066-C6BD-4C4B-99E0-FE5BDCE82C6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CB7F5A2-490F-473B-9B21-A89A8FF445B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8738,17 +10033,17 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
+      <xdr:colOff>12375</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>17530</xdr:rowOff>
+      <xdr:rowOff>6574</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="10071100" cy="7135381"/>
+    <xdr:ext cx="9635245" cy="7350667"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DE16833-E5FC-4DEC-93A2-F543330AFAF6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC6B6820-FEBD-46A1-9003-7928F1555344}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8776,21 +10071,23 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
+      <xdr:colOff>12375</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>17530</xdr:rowOff>
+      <xdr:rowOff>6574</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="10071100" cy="7135381"/>
+    <xdr:ext cx="9635245" cy="7350667"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A50F1E8A-4F76-4E10-AF58-6C5B62124E95}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -9091,15 +10388,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3067CFC-EA40-4B5B-B74F-10E93F9F15C7}">
-  <dimension ref="A1:B39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sayfa1"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="6.08984375" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" customWidth="1"/>
-    <col min="19" max="19" width="13.1796875" customWidth="1"/>
-    <col min="20" max="20" width="6.81640625" customWidth="1"/>
+    <col min="1" max="1" width="21.7265625" customWidth="1"/>
+    <col min="2" max="2" width="6.1796875" customWidth="1"/>
+    <col min="18" max="18" width="12.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -9115,25 +10411,366 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4113DB6B-769F-4E94-9ABD-4BA337E64728}">
-  <dimension ref="A1:B39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD94CFB6-F899-4D8D-B116-5C0543BAF8B7}">
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="6.08984375" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" customWidth="1"/>
-    <col min="19" max="19" width="13.1796875" customWidth="1"/>
-    <col min="20" max="20" width="6.81640625" customWidth="1"/>
+    <col min="1" max="1" width="21.7265625" customWidth="1"/>
+    <col min="2" max="2" width="6.1796875" customWidth="1"/>
+    <col min="18" max="18" width="12.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -9149,25 +10786,366 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{870247E1-7303-4C19-A08B-D6FB23BBF452}">
-  <dimension ref="A1:B39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992653B0-0CB2-422C-919E-E143FEB97CE6}">
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="6.08984375" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" customWidth="1"/>
-    <col min="19" max="19" width="13.1796875" customWidth="1"/>
-    <col min="20" max="20" width="6.81640625" customWidth="1"/>
+    <col min="1" max="1" width="21.7265625" customWidth="1"/>
+    <col min="2" max="2" width="6.1796875" customWidth="1"/>
+    <col min="18" max="18" width="12.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -9183,25 +11161,366 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA4D0F1-0E39-4A26-A53C-DA58723D6A74}">
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="6.08984375" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" customWidth="1"/>
-    <col min="19" max="19" width="13.1796875" customWidth="1"/>
-    <col min="20" max="20" width="6.81640625" customWidth="1"/>
+    <col min="1" max="1" width="21.7265625" customWidth="1"/>
+    <col min="2" max="2" width="6.1796875" customWidth="1"/>
+    <col min="18" max="18" width="12.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -9217,11 +11536,354 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" ht="27.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>